--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderDemand.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderDemand.xlsx
@@ -92,7 +92,7 @@
     <t>{.virtualUsableQty}</t>
   </si>
   <si>
-    <t>{.isVirtualScarce}</t>
+    <t>{.isVirtualScarceName}</t>
   </si>
   <si>
     <t>{.virtualScarceQty}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderDemand.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderDemand.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>虚拟仓</t>
   </si>
@@ -62,6 +62,9 @@
     <t xml:space="preserve">缺货数量 </t>
   </si>
   <si>
+    <t>实体仓未分配</t>
+  </si>
+  <si>
     <t>更新时间</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
   </si>
   <si>
     <t>{.virtualScarceQty}</t>
+  </si>
+  <si>
+    <t>{.unDistributionQty}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
@@ -1029,7 +1035,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -1043,10 +1049,10 @@
     <col min="9" max="9" width="14.125" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
     <col min="11" max="11" width="13.375" customWidth="1"/>
-    <col min="12" max="12" width="17.125" customWidth="1"/>
+    <col min="12" max="13" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1083,43 +1089,49 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
